--- a/data.xlsx
+++ b/data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://crtnepal-my.sharepoint.com/personal/shinza_crtnepal_org/Documents/Power GIF/Dashboard/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Acer\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="639" documentId="13_ncr:1_{BECC5A93-8A29-40DD-AE45-598F0E557E2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4ABCECE5-2AF3-4B0A-ABD2-2EE0517B8732}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB8164B5-FD6E-4225-9E82-EF1F1442324C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="HOW TO USE" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
   <externalReferences>
     <externalReference r:id="rId6"/>
   </externalReferences>
-  <calcPr calcId="191029" calcCompleted="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -663,7 +663,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Main"/>
@@ -1304,7 +1304,7 @@
         <v>108</v>
       </c>
       <c r="B4" s="13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C4" s="19">
         <v>120</v>
@@ -1484,7 +1484,7 @@
         <v>125</v>
       </c>
       <c r="B14" s="12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C14" s="12">
         <v>50</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Acer\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://crtnepal-my.sharepoint.com/personal/shinza_crtnepal_org/Documents/Power GIF/Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB8164B5-FD6E-4225-9E82-EF1F1442324C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="640" documentId="13_ncr:1_{BECC5A93-8A29-40DD-AE45-598F0E557E2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ECE69AD3-68AC-4A0E-A214-C629DC886FBD}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="HOW TO USE" sheetId="1" r:id="rId1"/>
@@ -663,7 +663,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Main"/>
@@ -1304,7 +1304,7 @@
         <v>108</v>
       </c>
       <c r="B4" s="13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C4" s="19">
         <v>120</v>
@@ -1484,7 +1484,7 @@
         <v>125</v>
       </c>
       <c r="B14" s="12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C14" s="12">
         <v>50</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://crtnepal-my.sharepoint.com/personal/shinza_crtnepal_org/Documents/Power GIF/Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="640" documentId="13_ncr:1_{BECC5A93-8A29-40DD-AE45-598F0E557E2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ECE69AD3-68AC-4A0E-A214-C629DC886FBD}"/>
+  <xr:revisionPtr revIDLastSave="643" documentId="13_ncr:1_{BECC5A93-8A29-40DD-AE45-598F0E557E2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0945C3B2-8E73-47EA-852D-C87DF9FB6786}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="HOW TO USE" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="135">
   <si>
     <t>POWER-GIF MEAL Dashboard — Excel Data File</t>
   </si>
@@ -440,6 +440,9 @@
   </si>
   <si>
     <t xml:space="preserve">Collaboration with like minded projects working under decarbonization of industries. </t>
+  </si>
+  <si>
+    <t>CNI/Power -GIF</t>
   </si>
 </sst>
 </file>
@@ -668,7 +671,7 @@
     <sheetNames>
       <sheetName val="Main"/>
       <sheetName val="Summary"/>
-      <sheetName val="Revised"/>
+      <sheetName val="Revised_19 Aug 2026"/>
       <sheetName val="Plan till August"/>
     </sheetNames>
     <sheetDataSet>
@@ -720,7 +723,7 @@
         </row>
         <row r="97">
           <cell r="I97">
-            <v>20.75</v>
+            <v>22.75</v>
           </cell>
         </row>
         <row r="105">
@@ -730,7 +733,7 @@
         </row>
         <row r="118">
           <cell r="I118">
-            <v>2</v>
+            <v>58</v>
           </cell>
         </row>
         <row r="124">
@@ -775,7 +778,7 @@
         </row>
         <row r="175">
           <cell r="I175">
-            <v>0.75</v>
+            <v>15</v>
           </cell>
         </row>
         <row r="181">
@@ -2272,7 +2275,7 @@
       </c>
       <c r="D13" s="15">
         <f>[1]Main!$I$97</f>
-        <v>20.75</v>
+        <v>22.75</v>
       </c>
       <c r="E13" s="15"/>
     </row>
@@ -2304,7 +2307,7 @@
       </c>
       <c r="D15" s="15">
         <f>[1]Main!$I$118</f>
-        <v>2</v>
+        <v>58</v>
       </c>
       <c r="E15" s="15"/>
     </row>
@@ -2448,7 +2451,7 @@
       </c>
       <c r="D24" s="15">
         <f>[1]Main!$I$175</f>
-        <v>0.75</v>
+        <v>15</v>
       </c>
       <c r="E24" s="13"/>
     </row>
@@ -2607,7 +2610,7 @@
         <v>128</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>73</v>
+        <v>134</v>
       </c>
       <c r="E4" s="8"/>
     </row>
@@ -2620,7 +2623,7 @@
         <v>128</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>73</v>
+        <v>134</v>
       </c>
       <c r="E5" s="7"/>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://crtnepal-my.sharepoint.com/personal/shinza_crtnepal_org/Documents/Power GIF/Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="643" documentId="13_ncr:1_{BECC5A93-8A29-40DD-AE45-598F0E557E2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0945C3B2-8E73-47EA-852D-C87DF9FB6786}"/>
+  <xr:revisionPtr revIDLastSave="644" documentId="13_ncr:1_{BECC5A93-8A29-40DD-AE45-598F0E557E2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{807EE14A-33FB-40D9-894F-76B2E325E225}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="HOW TO USE" sheetId="1" r:id="rId1"/>
@@ -18,9 +18,10 @@
     <sheet name="Outcomes" sheetId="3" r:id="rId3"/>
     <sheet name="Activities" sheetId="4" r:id="rId4"/>
     <sheet name="Risks" sheetId="5" r:id="rId5"/>
+    <sheet name="Learning" sheetId="6" r:id="rId6"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId6"/>
+    <externalReference r:id="rId7"/>
   </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="145">
   <si>
     <t>POWER-GIF MEAL Dashboard — Excel Data File</t>
   </si>
@@ -443,13 +444,43 @@
   </si>
   <si>
     <t>CNI/Power -GIF</t>
+  </si>
+  <si>
+    <t>Learning and Insights</t>
+  </si>
+  <si>
+    <t>Exactly three rows, in this order. Row 4 = Key Learning, row 5 = Action Required, row 6 = Data Quality Notes. Column A is a label for you; only column B is displayed.</t>
+  </si>
+  <si>
+    <t>Field</t>
+  </si>
+  <si>
+    <t>Text shown on the dashboard</t>
+  </si>
+  <si>
+    <t>Key Learning</t>
+  </si>
+  <si>
+    <t>Industries respond faster to audit requests routed through CNI membership channels than to direct approaches.</t>
+  </si>
+  <si>
+    <t>Action Required</t>
+  </si>
+  <si>
+    <t>Bring the installer training component forward to Year 1 to avoid a bottleneck at pilot installation stage.</t>
+  </si>
+  <si>
+    <t>Data Quality Notes</t>
+  </si>
+  <si>
+    <t>NEA TOD billing data for two corridor industries is incomplete for FY 2082; figures are provisional pending reconciliation.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -503,6 +534,26 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color rgb="FF1B5E37"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FF7A7468"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -537,7 +588,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -580,11 +631,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -648,6 +714,14 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2821,4 +2895,64 @@
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7B1D4F6-49BC-4E56-887D-EE7D98A3F513}">
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="24" customWidth="1"/>
+    <col min="2" max="2" width="88" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="23" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="24" t="s">
+        <v>136</v>
+      </c>
+      <c r="B2" s="22"/>
+    </row>
+    <row r="3" spans="1:2" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="25" t="s">
+        <v>137</v>
+      </c>
+      <c r="B3" s="25" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="26" t="s">
+        <v>139</v>
+      </c>
+      <c r="B4" s="26" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="26" t="s">
+        <v>141</v>
+      </c>
+      <c r="B5" s="26" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="26" t="s">
+        <v>143</v>
+      </c>
+      <c r="B6" s="26" t="s">
+        <v>144</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:B2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>